--- a/outputs/evaluation/architecture/validation/gemini-3-5/CF_M06/run_3/CF_M06_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/validation/gemini-3-5/CF_M06/run_3/CF_M06_arch_eval.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -456,7 +461,10 @@
       <c r="C2" t="n">
         <v>0.6667</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>0.5854</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -475,6 +483,9 @@
         <v>0.7931</v>
       </c>
       <c r="D3" t="n">
+        <v>0.6479</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.9645</v>
       </c>
     </row>
@@ -491,6 +502,9 @@
         <v>0.1429</v>
       </c>
       <c r="D4" t="n">
+        <v>0.1818</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.83</v>
       </c>
     </row>
@@ -1221,14 +1235,11 @@
           <t>45</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>AU_25</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Presentation</t>
@@ -1252,13 +1263,11 @@
           <t>CF_M06_P01</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M06_AU03</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1304,13 +1313,11 @@
           <t>['P_01']</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>P_02</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Three Layers</t>
@@ -1334,13 +1341,11 @@
           <t>CF_M06_AU23</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M06_P01</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1381,14 +1386,11 @@
           <t>45</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>AU_27</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Data</t>
@@ -1412,13 +1414,11 @@
           <t>CF_M06_P01</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M06_AU05</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1439,7 +1439,6 @@
       <c r="D5" t="n">
         <v>0.83</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1460,7 +1459,6 @@
           <t>['AU_05', 'AU_29']</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>AU_38</t>
@@ -1471,7 +1469,6 @@
           <t>waapiti server, websocket</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1490,7 +1487,6 @@
           <t>CF_M06_AU23, CF_M06_AU02</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M06_AU30</t>
@@ -1541,14 +1537,11 @@
           <t>45</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>AU_26</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Domain</t>
@@ -1572,13 +1565,11 @@
           <t>CF_M06_P01</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M06_AU04</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1624,13 +1615,11 @@
           <t>['AU_30', 'AU_39']</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>AU_32</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Apple Push Notification Service</t>
@@ -1649,14 +1638,11 @@
       <c r="P7" t="n">
         <v>91</v>
       </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M06_AU21</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1702,13 +1688,11 @@
           <t>['AU_30', 'AU_39']</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>AU_31</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Firebase Cloud Messaging</t>
@@ -1727,14 +1711,11 @@
       <c r="P8" t="n">
         <v>91</v>
       </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M06_AU20</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1775,14 +1756,11 @@
           <t>45</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>AU_06</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Mobile device</t>
@@ -1801,14 +1779,11 @@
       <c r="P9" t="n">
         <v>45</v>
       </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M06_AU01</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1849,14 +1824,11 @@
           <t>49</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>P_05</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Decorator Pattern</t>
@@ -1880,13 +1852,11 @@
           <t>CF_M06_AU23</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M06_P04</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1927,14 +1897,11 @@
           <t>46</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>AU_11</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>React Native</t>
@@ -1958,13 +1925,11 @@
           <t>CF_M06_AU23</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M06_AU06</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2005,14 +1970,11 @@
           <t>51</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>AU_12</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>React</t>
@@ -2036,13 +1998,11 @@
           <t>CF_M06_AU23</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M06_AU14</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2083,14 +2043,11 @@
           <t>49</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>P_06</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Lazy Loading</t>
@@ -2114,13 +2071,11 @@
           <t>CF_M06_AU23</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CF_M06_P05</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2161,14 +2116,11 @@
           <t>47</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>AU_09</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Dispatcher</t>
@@ -2192,13 +2144,11 @@
           <t>CF_M06_P02</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>CF_M06_AU09</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2239,14 +2189,11 @@
           <t>51</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>AU_14</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Jest</t>
@@ -2270,13 +2217,11 @@
           <t>CF_M06_AU23</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>CF_M06_AU16</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2317,14 +2262,11 @@
           <t>45</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>AU_22</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>HTTP</t>
@@ -2348,13 +2290,11 @@
           <t>CF_M06_AU26</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>CF_M06_AU29</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2400,13 +2340,11 @@
           <t>['P_03']</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>P_04</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Observer Pattern</t>
@@ -2430,13 +2368,11 @@
           <t>CF_M06_P02</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>CF_M06_P03</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2477,14 +2413,11 @@
           <t>45</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>AU_05</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Waapiti Server</t>
@@ -2503,14 +2436,11 @@
       <c r="P18" t="n">
         <v>45</v>
       </c>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>CF_M06_AU02</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2551,14 +2481,11 @@
           <t>46</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>AU_07</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>Store</t>
@@ -2582,13 +2509,11 @@
           <t>CF_M06_P02</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>CF_M06_AU07</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2629,14 +2554,11 @@
           <t>51</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>AU_13</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>Expo</t>
@@ -2660,13 +2582,11 @@
           <t>CF_M06_AU23</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>CF_M06_AU15</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2707,14 +2627,11 @@
           <t>51</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>AU_15</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>NodeJS</t>
@@ -2733,14 +2650,11 @@
       <c r="P21" t="n">
         <v>51</v>
       </c>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>CF_M06_AU17</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2781,14 +2695,11 @@
           <t>52</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>AU_17</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>NestJS</t>
@@ -2807,14 +2718,11 @@
       <c r="P22" t="n">
         <v>51</v>
       </c>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>CF_M06_AU19</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2855,14 +2763,11 @@
           <t>46</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>P_03</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>Flux</t>
@@ -2886,13 +2791,11 @@
           <t>CF_M06_AU23</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>CF_M06_P02</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2933,14 +2836,11 @@
           <t>47</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>AU_08</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>Action</t>
@@ -2964,13 +2864,11 @@
           <t>CF_M06_P02</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>CF_M06_AU08</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3011,14 +2909,11 @@
           <t>51</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>AU_16</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>TypeScript</t>
@@ -3037,14 +2932,11 @@
       <c r="P25" t="n">
         <v>51</v>
       </c>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>CF_M06_AU18</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3118,7 +3010,6 @@
           <t>Partners</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Els usuaris finals d’aquest projecte són els partners.</t>
@@ -3154,7 +3045,6 @@
           <t>Waapiti</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Waapiti és una empresa tecnològica que es dedica en aquest àmbit.</t>
@@ -3190,7 +3080,6 @@
           <t>Players</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Players: són equips informàtics que fan la funció d’intermediari entre la plataforma de Waapiti i el suport audiovisual en si, permetent així la sincronització i reproducció dels continguts dels clients.</t>
@@ -3226,7 +3115,6 @@
           <t>Locations</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Locations: fan referència a l’adreça física dels players, a la localització d’aquests.</t>
@@ -3262,7 +3150,6 @@
           <t>Reducers</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Els canvis es fan amb funcions pures: els Reducers són funcions pures que reben l’estat actual de l’aplicació i l’acció a realitzar i retornen un nou estat, senza modificar directament l’estat actual.</t>
@@ -3298,7 +3185,6 @@
           <t>Visual Studio Code</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Visual Studio Code: és un editor de codi font desenvolupar per Microsoft.</t>
@@ -3334,7 +3220,6 @@
           <t>GIT</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>GIT: és un sistema de control de versions de codi font.</t>
@@ -3370,7 +3255,6 @@
           <t>React Navigation</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Per a la navegació s’utilitza la llibreria React Navigation, que ofereix la transició entre pantalles de forma senzilla i un historial de navegació.</t>
@@ -3406,7 +3290,6 @@
           <t>react-native-async-storage</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Per a la gestió de la sessió s’utilitza la llibreria react-native-async-storage, que ens permet guardar parells de clau-valor de manera local en els dispositius.</t>
@@ -3442,7 +3325,6 @@
           <t>Storage Service</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>És el servidor que s’encarrega de comunicar-se amb la base de dades i altres serveis allotjats a AWS.</t>
@@ -3478,7 +3360,6 @@
           <t>AWS</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>És el servidor que s’encarrega de comunicar-se amb la base de dades i altres serveis allotjats a AWS.</t>
@@ -3514,7 +3395,6 @@
           <t>Google Maps API</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>S’utilitza l’API de Google Maps per tal de facilitar la búsqueda d’adreça</t>
@@ -3525,7 +3405,6 @@
           <t>CF_M06_AU27</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>0.6421</v>
       </c>
@@ -3546,7 +3425,6 @@
           <t>WebSocket</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Aquesta funcionalitat es connecta via socket amb el servidor i mostra el contingut segons els missatges que aquest envia.</t>
@@ -3582,7 +3460,6 @@
           <t>Messaging Service</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>Per poder implementar aquesta funcionalitat és necessari utilitzar un servei de missatgeria per cada plataforma: Firebase Cloud Messaging (FCM) per dispositius Android i Apple Push Notification Service (APNS) per dispositius iOS.</t>
@@ -3618,7 +3495,6 @@
           <t>Expo Push API</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>Expo Push API és un servei que facilita la implementació de les notificacions push ja que es delega tota la configuració al servei.</t>
@@ -3654,7 +3530,6 @@
           <t>Notification Service</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>Així mateix es necessita un servei de notificacions que es comuniqui amb aquestes.</t>
@@ -3690,7 +3565,6 @@
           <t>Amazon Simple Notification Service (Amazon SNS)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>Amazon Simple Notification Service (Amazon SNS) és un servei administrat el qual ofereix el lliurament de missatges dels publicadors als subscriptors</t>
@@ -3726,7 +3600,6 @@
           <t>expo-notifications</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>Per altra banda, per rebre les notificacions s’utilitza la llibreria expo-notifications el qual ofereix una API per a la gestió de notificacions.</t>
@@ -3757,7 +3630,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>waapiti server, google maps api</t>
@@ -3773,7 +3645,6 @@
           <t>CF_M06_AU27</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>0.6384</v>
       </c>
@@ -3789,7 +3660,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>messaging service, firebase cloud messaging (fcm), apple push notification service (apns)</t>
@@ -3825,7 +3695,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>notification service, messaging service</t>
@@ -3866,7 +3735,6 @@
           <t>Client-Server</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>L’arquitectura física de la solució està format per un dispositiu mòbil, ja sigui sistema iOS o Android, i el servidor de l’empresa. Aquesta interactuarà amb l’API de Waapiti mitjançant peticions HTTP.</t>
@@ -3877,7 +3745,6 @@
           <t>CF_M06_AU30</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>0.7382</v>
       </c>
@@ -3949,7 +3816,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>action, store</t>
@@ -3985,7 +3851,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>dispatcher, store</t>
@@ -4001,7 +3866,6 @@
           <t>AU_40</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>0.6706</v>
       </c>
@@ -4022,7 +3886,6 @@
           <t>User</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>As already mentioned, there are third-party companies that offer digital signage consulting using Waapiti technology. They are end users of this project.</t>
@@ -4053,7 +3916,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>presentation, user</t>
@@ -4094,7 +3956,6 @@
           <t>AWS SNS</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>In the end it was decided to use AWS SNS due to the cost compared to Expo Push API. In addition, AWS SNS is more scalable and can be used by other services.</t>
@@ -4130,7 +3991,6 @@
           <t>Mobile Application</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>The project “Development of a mobile application for a digital signage company”</t>
@@ -4166,7 +4026,6 @@
           <t>Player</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t xml:space="preserve">these are computer equipment that act as an intermediary between the Waapiti platform and the audiovisual media itself, thus allowing the synchronization or reproduction of client
@@ -4203,7 +4062,6 @@
           <t>Redux</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Redux [19] is a library used to manage application state. It is inspired by the Flux architecture, but with a simpler implementation.</t>
@@ -4234,7 +4092,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>waapiti server, mobile application</t>
@@ -4271,7 +4128,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>mobile device, waapiti server</t>
@@ -4307,7 +4163,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>waapiti server, data</t>
@@ -4348,7 +4203,6 @@
           <t>Socket</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>the content according to the messages that it sends.</t>
